--- a/Outputs/Scenarios/PtX_demand_FI_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_FI_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.002049293468758665</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01325058567698225</v>
+        <v>0.007225934957707601</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.004416861892327416</v>
+        <v>0.01040086215275063</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>2.952685001275128e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.004416861892327416</v>
+        <v>0.004457512351178842</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.003033729486396468</v>
       </c>
       <c r="K30" t="n">
-        <v>0.07148874739172903</v>
+        <v>0.0389849212294041</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.02382958246390968</v>
+        <v>0.05611409376310102</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0001596699729682351</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02382958246390968</v>
+        <v>0.02404889732704329</v>
       </c>
     </row>
     <row r="43">
